--- a/ig-pub/demo.ig/all-profiles.xlsx
+++ b/ig-pub/demo.ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T14:02:19+01:00</t>
+    <t>2026-01-06T16:32:59+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
